--- a/demo/excel/demo-MX.xlsx
+++ b/demo/excel/demo-MX.xlsx
@@ -9,12 +9,14 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scenarios" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codes" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Scenarios'!$A$1:$F$33</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Reference'!$A$1:$I$90</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Read me'!$A$1:$B$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Scenarios'!$A$1:$F$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Reference'!$A$1:$J$90</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Codes'!$A$1:$F$159</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Read me'!$A$1:$B$22</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -447,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -696,7 +698,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>XS0000000001</t>
+          <t>XS0000000009</t>
         </is>
       </c>
     </row>
@@ -868,7 +870,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>/Document/SctiesSttlmTxInstr/DlvrgSttlmPties/Pty1/Id/AnyBIC</t>
+          <t>/Document/SctiesSttlmTxInstr/SttlmAmt/Amt</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -876,7 +878,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>DEMODEAGXXX</t>
+          <t>USD 25000.00</t>
         </is>
       </c>
     </row>
@@ -898,7 +900,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>/Document/SctiesSttlmTxInstr/SttlmAmt/Amt</t>
+          <t>/Document/SctiesSttlmTxInstr/SttlmAmt/CdtDbtInd</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -906,19 +908,19 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>USD 25000.00</t>
+          <t>DBIT</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>TC001</t>
+          <t>TC002</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>sese.023</t>
+          <t>sese.024</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -928,7 +930,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>/Document/SctiesSttlmTxInstr/SttlmAmt/CdtDbtInd</t>
+          <t>/Document/SctiesSttlmTxStsAdvc/TxIdDtls/SctiesMvmntTp</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -936,7 +938,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>DBIT</t>
+          <t>RECE</t>
         </is>
       </c>
     </row>
@@ -958,7 +960,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>/Document/SctiesSttlmTxStsAdvc/TxIdDtls/SctiesMvmntTp</t>
+          <t>/Document/SctiesSttlmTxStsAdvc/TxIdDtls/Pmt</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -966,7 +968,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>RECE</t>
+          <t>APMT</t>
         </is>
       </c>
     </row>
@@ -988,7 +990,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>/Document/SctiesSttlmTxStsAdvc/TxIdDtls/Pmt</t>
+          <t>/Document/SctiesSttlmTxStsAdvc/TxIdDtls/AcctOwnrTxId</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -996,7 +998,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>APMT</t>
+          <t>TEST001</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1020,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>/Document/SctiesSttlmTxStsAdvc/TxIdDtls/AcctOwnrTxId</t>
+          <t>/Document/SctiesSttlmTxStsAdvc/PrcgSts/AckdAccptd/NoSpcfdRsn</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -1026,19 +1028,19 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>TEST001</t>
+          <t>NORE</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>TC002</t>
+          <t>TC003</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>sese.024</t>
+          <t>sese.025</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1048,7 +1050,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>/Document/SctiesSttlmTxStsAdvc/PrcgSts/AckdAccptd/NoSpcfdRsn</t>
+          <t>/Document/SctiesSttlmTxConf/TxIdDtls/SctiesMvmntTp</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -1056,7 +1058,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>NORE</t>
+          <t>RECE</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1080,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>/Document/SctiesSttlmTxConf/TxIdDtls/SctiesMvmntTp</t>
+          <t>/Document/SctiesSttlmTxConf/TxIdDtls/Pmt</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -1086,7 +1088,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>RECE</t>
+          <t>APMT</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1110,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>/Document/SctiesSttlmTxConf/TxIdDtls/Pmt</t>
+          <t>/Document/SctiesSttlmTxConf/TxIdDtls/AcctOwnrTxId</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -1116,7 +1118,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>APMT</t>
+          <t>TEST001</t>
         </is>
       </c>
     </row>
@@ -1138,7 +1140,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>/Document/SctiesSttlmTxConf/TxIdDtls/AcctOwnrTxId</t>
+          <t>/Document/SctiesSttlmTxConf/TradDtls/TradDt/Dt/Dt</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -1146,7 +1148,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>TEST001</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1170,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>/Document/SctiesSttlmTxConf/TradDtls/TradDt/Dt/Dt</t>
+          <t>/Document/SctiesSttlmTxConf/TradDtls/FctvSttlmDt/Dt/Dt</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -1176,7 +1178,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
@@ -1198,7 +1200,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>/Document/SctiesSttlmTxConf/TradDtls/FctvSttlmDt/Dt/Dt</t>
+          <t>/Document/SctiesSttlmTxConf/FinInstrmId/ISIN</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -1206,7 +1208,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>XS0000000009</t>
         </is>
       </c>
     </row>
@@ -1228,7 +1230,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>/Document/SctiesSttlmTxConf/FinInstrmId/ISIN</t>
+          <t>/Document/SctiesSttlmTxConf/QtyAndAcctDtls/SttlmQty/Qty/Unit</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -1236,7 +1238,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>XS0000000001</t>
+          <t>1000</t>
         </is>
       </c>
     </row>
@@ -1258,7 +1260,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>/Document/SctiesSttlmTxConf/QtyAndAcctDtls/SttlmQty/Qty/Unit</t>
+          <t>/Document/SctiesSttlmTxConf/QtyAndAcctDtls/SfkpgAcct/Id</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -1266,7 +1268,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>SAFE0000001</t>
         </is>
       </c>
     </row>
@@ -1288,7 +1290,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>/Document/SctiesSttlmTxConf/QtyAndAcctDtls/SfkpgAcct/Id</t>
+          <t>/Document/SctiesSttlmTxConf/SttlmParams/SctiesTxTp/Cd</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -1296,7 +1298,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>SAFE0000001</t>
+          <t>TRAD</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1320,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>/Document/SctiesSttlmTxConf/SttlmParams/SctiesTxTp/Cd</t>
+          <t>/Document/SctiesSttlmTxConf/DlvrgSttlmPties/Dpstry/Id/AnyBIC</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -1326,7 +1328,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>TRAD</t>
+          <t>DEMOGB2LXXX</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1350,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>/Document/SctiesSttlmTxConf/DlvrgSttlmPties/Dpstry/Id/AnyBIC</t>
+          <t>/Document/SctiesSttlmTxConf/SttlmAmt/Amt</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -1356,7 +1358,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>DEMOGB2LXXX</t>
+          <t>USD 25000.00</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1380,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>/Document/SctiesSttlmTxConf/DlvrgSttlmPties/Pty1/Id/AnyBIC</t>
+          <t>/Document/SctiesSttlmTxConf/SttlmAmt/CdtDbtInd</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -1386,72 +1388,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>DEMODEAGXXX</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>TC003</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>sese.025</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>BASE_DEMO_V1</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>/Document/SctiesSttlmTxConf/SttlmAmt/Amt</t>
-        </is>
-      </c>
-      <c r="E32" t="n">
-        <v>1</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>USD 25000.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>TC003</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>sese.025</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>BASE_DEMO_V1</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>/Document/SctiesSttlmTxConf/SttlmAmt/CdtDbtInd</t>
-        </is>
-      </c>
-      <c r="E33" t="n">
-        <v>1</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
           <t>DBIT</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F33"/>
+  <autoFilter ref="A1:F31"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1462,18 +1404,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I90"/>
+  <dimension ref="A1:J90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="67" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="49" customWidth="1" min="4" max="4"/>
-    <col width="25" customWidth="1" min="5" max="5"/>
-    <col width="70" customWidth="1" min="6" max="6"/>
-    <col width="49" customWidth="1" min="7" max="7"/>
-    <col width="70" customWidth="1" min="8" max="8"/>
-    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="70" customWidth="1" min="7" max="7"/>
+    <col width="49" customWidth="1" min="8" max="8"/>
+    <col width="70" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1499,25 +1442,30 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Input kind</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Data type</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Format</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Example</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Allowed codes</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Max occurrences</t>
         </is>
@@ -1546,21 +1494,26 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
           <t>Max35Text</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Up to 35 characters.</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>CXLADV0000001</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr"/>
-      <c r="I2" s="2" t="n">
+      <c r="I2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1587,21 +1540,26 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
           <t>Max35Text</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Up to 35 characters.</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>TESTREF001</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr"/>
-      <c r="I3" s="2" t="n">
+      <c r="I3" s="2" t="inlineStr"/>
+      <c r="J3" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1628,21 +1586,26 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>ISODateTime</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>An ISO date and time, YYYY-MM-DDThh:mm:ss with an optional zone.</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>2026-08-16T09:30:00Z</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="n">
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1669,21 +1632,26 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>Max35Text</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>Up to 35 characters.</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>TESTREF001</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="n">
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1710,21 +1678,26 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>Max35Text</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>Up to 35 characters.</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>SVCR000000001</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="n">
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1751,25 +1724,30 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>SELECT</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>Code</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>One of: RECE, DELI</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>RECE</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>RECE, DELI</t>
         </is>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1796,21 +1774,26 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>Max35Text</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>Up to 35 characters.</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>SAFE0000001</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="n">
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1837,21 +1820,26 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t>Max350Text</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>Up to 350 characters.</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>SENT IN ERROR - DUPLICATE OF TESTREF000</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="n">
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1878,21 +1866,26 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>Max35Text</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>Up to 35 characters. Keep it unique for the sending party.</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>TESTREF001</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr"/>
-      <c r="I10" s="2" t="n">
+      <c r="I10" s="2" t="inlineStr"/>
+      <c r="J10" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1919,25 +1912,30 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
+          <t>SELECT</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>Code</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>RECE to receive securities; DELI to deliver securities.</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>RECE</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>RECE, DELI</t>
         </is>
       </c>
-      <c r="I11" s="2" t="n">
+      <c r="J11" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1964,25 +1962,30 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>SELECT</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>Code</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>APMT for against payment; FREE for free of payment.</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>APMT</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>APMT, FREE</t>
         </is>
       </c>
-      <c r="I12" s="2" t="n">
+      <c r="J12" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2009,21 +2012,26 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
           <t>Max35Text</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>Up to 35 characters.</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>COMMONREF001</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="n">
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2050,21 +2058,26 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
+          <t>DATE</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
           <t>ISODate</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>An ISO date, YYYY-MM-DD.</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="n">
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2091,21 +2104,26 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
+          <t>DATE</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
           <t>ISODate</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>An ISO date, YYYY-MM-DD.</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr"/>
-      <c r="I15" s="2" t="n">
+      <c r="I15" s="2" t="inlineStr"/>
+      <c r="J15" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2132,21 +2150,26 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>IDENTIFIER</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>ISINOct2015Identifier</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>A 12-character ISIN: 2 letters, 9 alphanumerics and a check digit.</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>XS0000000001</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr"/>
-      <c r="I16" s="2" t="n">
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>XS0000000009</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr"/>
+      <c r="J16" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2173,21 +2196,26 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
           <t>Max140Text</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>Up to 140 characters.</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>SYNTHETIC TEST BOND 2030</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="n">
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2214,21 +2242,26 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
+          <t>QUANTITY</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>DecimalNumber</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>A positive decimal using a full stop as the decimal separator, for example 1000 or 1000.5.</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr"/>
-      <c r="I18" s="2" t="n">
+      <c r="I18" s="2" t="inlineStr"/>
+      <c r="J18" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2255,21 +2288,26 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
           <t>Max35Text</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>Up to 35 characters.</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>SAFE0000001</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr"/>
-      <c r="I19" s="2" t="n">
+      <c r="I19" s="2" t="inlineStr"/>
+      <c r="J19" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2296,25 +2334,30 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
+          <t>SELECT</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>Code</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>A four-letter code from the configured subset. TRAD covers an ordinary secondary-market trade.</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>TRAD</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>TRAD, COLI, COLO, PLAC, PORT, REDM, SUBS, TURN, NETT, OWNE, OWNI</t>
         </is>
       </c>
-      <c r="I20" s="2" t="n">
+      <c r="J20" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2341,25 +2384,30 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
+          <t>SELECT</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
           <t>Code</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>One of: NOMC, PART, PARC, PARQ, ASGN, BLOC, CLEN, DIRT, DLWM, PHYS, SPDL</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>NOMC</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>NOMC, PART, PARC, PARQ, ASGN, BLOC, CLEN, DIRT, DLWM, PHYS, SPDL</t>
         </is>
       </c>
-      <c r="I21" t="n">
+      <c r="J21" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2386,21 +2434,26 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
+          <t>PARTY_BIC</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
           <t>AnyBICDec2014Identifier</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>An 8- or 11-character BIC.</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>DEMOGB2LXXX</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="n">
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2427,21 +2480,26 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
+          <t>PARTY_BIC</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
           <t>AnyBICDec2014Identifier</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>An 8- or 11-character BIC.</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>DEMODEAGXXX</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="n">
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2468,21 +2526,26 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
+          <t>PARTY_BIC</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
           <t>AnyBICDec2014Identifier</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>An 8- or 11-character BIC.</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>DEMOGB2LXXX</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="n">
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2509,21 +2572,26 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
+          <t>PARTY_BIC</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
           <t>AnyBICDec2014Identifier</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>An 8- or 11-character BIC.</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>DEMOREAGXXX</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="n">
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2550,21 +2618,26 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
+          <t>AMOUNT</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
           <t>ActiveCurrencyAndAmount</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>Enter as CURRENCY AMOUNT, for example "USD 25000.00". The composer writes Ccy="USD" and the amount 25000.00.</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>USD 25000.00</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="n">
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2591,25 +2664,30 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
+          <t>SELECT</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
           <t>Code</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>CRDT when cash is received; DBIT when cash is paid away.</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>DBIT</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>CRDT, DBIT</t>
         </is>
       </c>
-      <c r="I27" t="n">
+      <c r="J27" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2636,25 +2714,30 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
+          <t>SELECT</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>Code</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>One of: RECE, DELI</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>RECE</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>RECE, DELI</t>
         </is>
       </c>
-      <c r="I28" s="2" t="n">
+      <c r="J28" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2681,25 +2764,30 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
+          <t>SELECT</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
           <t>Code</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>One of: APMT, FREE</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>APMT</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr">
         <is>
           <t>APMT, FREE</t>
         </is>
       </c>
-      <c r="I29" s="2" t="n">
+      <c r="J29" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2726,21 +2814,26 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>Max35Text</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>Up to 35 characters.</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>TEST001</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr"/>
-      <c r="I30" s="2" t="n">
+      <c r="I30" s="2" t="inlineStr"/>
+      <c r="J30" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2767,21 +2860,26 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
           <t>Max35Text</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>Up to 35 characters.</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>SVCR000000001</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="n">
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2808,25 +2906,30 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
+          <t>SELECT</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
           <t>Code</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>One of: NORE</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>NORE</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>NORE</t>
         </is>
       </c>
-      <c r="I32" t="n">
+      <c r="J32" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2853,25 +2956,30 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
+          <t>SELECT</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
           <t>Code</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>One of: AWMO, AWSH, BATC, CAIS, CYCL, DOCC, DOCY, FUTU, LACK, LATE, NEXT, OTHR</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>LACK</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>AWMO, AWSH, BATC, CAIS, CYCL, DOCC, DOCY, FUTU, LACK, LATE, NEXT, OTHR</t>
         </is>
       </c>
-      <c r="I33" t="n">
+      <c r="J33" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2898,17 +3006,22 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
           <t>Max350Text</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>Up to 350 characters.</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
-      <c r="I34" t="n">
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2935,25 +3048,30 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
+          <t>SELECT</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
           <t>Code</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>One of: CASH, DDAT, DQUA, DSEC, ICAG, ICUS, IEXE, INVB, NCRR, REFE, SAFE, SETS, OTHR</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>DSEC</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>CASH, DDAT, DQUA, DSEC, ICAG, ICUS, IEXE, INVB, NCRR, REFE, SAFE, SETS, OTHR</t>
         </is>
       </c>
-      <c r="I35" t="n">
+      <c r="J35" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2980,21 +3098,26 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
           <t>Max350Text</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>Up to 350 characters.</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t>SYNTHETIC TEST REJECTION NARRATIVE</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="n">
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3021,25 +3144,30 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
+          <t>SELECT</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
           <t>Code</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>One of: CANI, CANS, CSUB, CANT, CANZ, CORP, SCEX, OTHR</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>CANI</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>CANI, CANS, CSUB, CANT, CANZ, CORP, SCEX, OTHR</t>
         </is>
       </c>
-      <c r="I37" t="n">
+      <c r="J37" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3066,25 +3194,30 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
+          <t>SELECT</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
           <t>Code</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>One of: MACH</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>MACH</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t>MACH</t>
         </is>
       </c>
-      <c r="I38" t="n">
+      <c r="J38" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3111,25 +3244,30 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
+          <t>SELECT</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
           <t>Code</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>One of: CMIS, DDAT, DDEA, DELN, DEPT, DMON, DQUA, DSEC, DTRD, NMAS, SAFE, OTHR</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>DDAT</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>CMIS, DDAT, DDEA, DELN, DEPT, DMON, DQUA, DSEC, DTRD, NMAS, SAFE, OTHR</t>
         </is>
       </c>
-      <c r="I39" t="n">
+      <c r="J39" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3156,25 +3294,30 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
+          <t>SELECT</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
           <t>Code</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>One of: AWMO, AWSH, CAIS, CLAC, CMON, CYCL, LACK, LATE, MONY, PREA, OTHR</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t>LACK</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t>AWMO, AWSH, CAIS, CLAC, CMON, CYCL, LACK, LATE, MONY, PREA, OTHR</t>
         </is>
       </c>
-      <c r="I40" t="n">
+      <c r="J40" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3201,25 +3344,30 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
+          <t>SELECT</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
           <t>Code</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>One of: AWMO, AWSH, CLAC, CMON, LACK, LATE, MONY, OTHR</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t>LACK</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t>AWMO, AWSH, CLAC, CMON, LACK, LATE, MONY, OTHR</t>
         </is>
       </c>
-      <c r="I41" t="n">
+      <c r="J41" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3246,25 +3394,30 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
+          <t>SELECT</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
           <t>Code</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr">
         <is>
           <t>One of: RECE, DELI</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr">
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>RECE</t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="I42" s="2" t="inlineStr">
         <is>
           <t>RECE, DELI</t>
         </is>
       </c>
-      <c r="I42" s="2" t="n">
+      <c r="J42" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3291,25 +3444,30 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
+          <t>SELECT</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
           <t>Code</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr">
         <is>
           <t>One of: APMT, FREE</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr">
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>APMT</t>
         </is>
       </c>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="I43" s="2" t="inlineStr">
         <is>
           <t>APMT, FREE</t>
         </is>
       </c>
-      <c r="I43" s="2" t="n">
+      <c r="J43" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3336,21 +3494,26 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
           <t>Max35Text</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr">
         <is>
           <t>Up to 35 characters.</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>TEST001</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr"/>
-      <c r="I44" s="2" t="n">
+      <c r="I44" s="2" t="inlineStr"/>
+      <c r="J44" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3377,21 +3540,26 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
+          <t>DATE</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
           <t>ISODate</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>An ISO date, YYYY-MM-DD.</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="n">
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3418,21 +3586,26 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
+          <t>DATE</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
           <t>ISODate</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>An ISO date, YYYY-MM-DD.</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="H46" t="inlineStr">
         <is>
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="n">
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3459,21 +3632,26 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
+          <t>DATE</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
           <t>ISODate</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr">
         <is>
           <t>An ISO date, YYYY-MM-DD.</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr">
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="H47" s="2" t="inlineStr"/>
-      <c r="I47" s="2" t="n">
+      <c r="I47" s="2" t="inlineStr"/>
+      <c r="J47" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3500,21 +3678,26 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
+          <t>IDENTIFIER</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
           <t>ISINOct2015Identifier</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr">
         <is>
           <t>A 12-character ISIN: 2 letters, 9 alphanumerics and a check digit.</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>XS0000000001</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr"/>
-      <c r="I48" s="2" t="n">
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>XS0000000009</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr"/>
+      <c r="J48" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3541,21 +3724,26 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
+          <t>QUANTITY</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
           <t>DecimalNumber</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr">
         <is>
           <t>A positive decimal using a full stop as the decimal separator.</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr">
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="H49" s="2" t="inlineStr"/>
-      <c r="I49" s="2" t="n">
+      <c r="I49" s="2" t="inlineStr"/>
+      <c r="J49" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3582,21 +3770,26 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
           <t>Max35Text</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr">
         <is>
           <t>Up to 35 characters.</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr">
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>SAFE0000001</t>
         </is>
       </c>
-      <c r="H50" s="2" t="inlineStr"/>
-      <c r="I50" s="2" t="n">
+      <c r="I50" s="2" t="inlineStr"/>
+      <c r="J50" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3623,25 +3816,30 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
+          <t>SELECT</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
           <t>Code</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr">
         <is>
           <t>One of: TRAD, COLI, COLO, PLAC, PORT, REDM, SUBS, TURN, NETT, OWNE, OWNI</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr">
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>TRAD</t>
         </is>
       </c>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="I51" s="2" t="inlineStr">
         <is>
           <t>TRAD, COLI, COLO, PLAC, PORT, REDM, SUBS, TURN, NETT, OWNE, OWNI</t>
         </is>
       </c>
-      <c r="I51" s="2" t="n">
+      <c r="J51" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3668,21 +3866,26 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
+          <t>PARTY_BIC</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
           <t>AnyBICDec2014Identifier</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="G52" t="inlineStr">
         <is>
           <t>An 8- or 11-character BIC.</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="H52" t="inlineStr">
         <is>
           <t>DEMOGB2LXXX</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="n">
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3709,21 +3912,26 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
+          <t>PARTY_BIC</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
           <t>AnyBICDec2014Identifier</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t>An 8- or 11-character BIC.</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="H53" t="inlineStr">
         <is>
           <t>DEMODEAGXXX</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="n">
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3750,21 +3958,26 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
+          <t>PARTY_BIC</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
           <t>AnyBICDec2014Identifier</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t>An 8- or 11-character BIC.</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="H54" t="inlineStr">
         <is>
           <t>DEMOGB2LXXX</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="n">
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3791,21 +4004,26 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
+          <t>PARTY_BIC</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
           <t>AnyBICDec2014Identifier</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="G55" t="inlineStr">
         <is>
           <t>An 8- or 11-character BIC.</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="H55" t="inlineStr">
         <is>
           <t>DEMOREAGXXX</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="n">
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3832,21 +4050,26 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
+          <t>AMOUNT</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
           <t>ActiveCurrencyAndAmount</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t>Enter as CURRENCY AMOUNT, for example "USD 25000.00".</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="H56" t="inlineStr">
         <is>
           <t>USD 25000.00</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="n">
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3873,25 +4096,30 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
+          <t>SELECT</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
           <t>Code</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t>One of: CRDT, DBIT</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="H57" t="inlineStr">
         <is>
           <t>DBIT</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="I57" t="inlineStr">
         <is>
           <t>CRDT, DBIT</t>
         </is>
       </c>
-      <c r="I57" t="n">
+      <c r="J57" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3918,21 +4146,26 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
           <t>Max35Text</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr">
         <is>
           <t>Up to 35 characters.</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr">
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>CXLREQ0000001</t>
         </is>
       </c>
-      <c r="H58" s="2" t="inlineStr"/>
-      <c r="I58" s="2" t="n">
+      <c r="I58" s="2" t="inlineStr"/>
+      <c r="J58" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3959,21 +4192,26 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
           <t>Max35Text</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr">
         <is>
           <t>Up to 35 characters.</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr">
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>TESTREF001</t>
         </is>
       </c>
-      <c r="H59" s="2" t="inlineStr"/>
-      <c r="I59" s="2" t="n">
+      <c r="I59" s="2" t="inlineStr"/>
+      <c r="J59" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4000,21 +4238,26 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
           <t>Max35Text</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
+      <c r="G60" t="inlineStr">
         <is>
           <t>Up to 35 characters.</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="H60" t="inlineStr">
         <is>
           <t>SVCR000000001</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="n">
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4041,25 +4284,30 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
+          <t>SELECT</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
           <t>Code</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
+      <c r="G61" t="inlineStr">
         <is>
           <t>One of: RECE, DELI</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="H61" t="inlineStr">
         <is>
           <t>RECE</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
+      <c r="I61" t="inlineStr">
         <is>
           <t>RECE, DELI</t>
         </is>
       </c>
-      <c r="I61" t="n">
+      <c r="J61" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4086,25 +4334,30 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
+          <t>SELECT</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
           <t>Code</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
+      <c r="G62" t="inlineStr">
         <is>
           <t>One of: APMT, FREE</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="H62" t="inlineStr">
         <is>
           <t>APMT</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
+      <c r="I62" t="inlineStr">
         <is>
           <t>APMT, FREE</t>
         </is>
       </c>
-      <c r="I62" t="n">
+      <c r="J62" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4131,21 +4384,26 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
+          <t>IDENTIFIER</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
           <t>ISINOct2015Identifier</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
+      <c r="G63" t="inlineStr">
         <is>
           <t>A 12-character ISIN: 2 letters, 9 alphanumerics and a check digit.</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>XS0000000001</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr"/>
-      <c r="I63" t="n">
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>XS0000000009</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4172,21 +4430,26 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
+          <t>QUANTITY</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
           <t>DecimalNumber</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
+      <c r="G64" t="inlineStr">
         <is>
           <t>A decimal number using a full stop as the decimal separator.</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
+      <c r="H64" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="n">
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4213,21 +4476,26 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
+          <t>DATE</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
           <t>ISODate</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
+      <c r="G65" t="inlineStr">
         <is>
           <t>An ISO date, YYYY-MM-DD.</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
+      <c r="H65" t="inlineStr">
         <is>
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr"/>
-      <c r="I65" t="n">
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4254,21 +4522,26 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
           <t>Max35Text</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
+      <c r="G66" t="inlineStr">
         <is>
           <t>Up to 35 characters.</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="H66" t="inlineStr">
         <is>
           <t>SAFE0000001</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr"/>
-      <c r="I66" t="n">
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4295,21 +4568,26 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
           <t>Max350Text</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
+      <c r="G67" t="inlineStr">
         <is>
           <t>Up to 350 characters.</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="H67" t="inlineStr">
         <is>
           <t>INSTRUCTED IN ERROR - WRONG SAFEKEEPING ACCOUNT</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr"/>
-      <c r="I67" t="n">
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4336,21 +4614,26 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
           <t>Max35Text</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr">
         <is>
           <t>Up to 35 characters.</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr">
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>MODREQ0000001</t>
         </is>
       </c>
-      <c r="H68" s="2" t="inlineStr"/>
-      <c r="I68" s="2" t="n">
+      <c r="I68" s="2" t="inlineStr"/>
+      <c r="J68" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4377,21 +4660,26 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
           <t>Max35Text</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr">
         <is>
           <t>Up to 35 characters.</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr">
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>TESTREF001</t>
         </is>
       </c>
-      <c r="H69" s="2" t="inlineStr"/>
-      <c r="I69" s="2" t="n">
+      <c r="I69" s="2" t="inlineStr"/>
+      <c r="J69" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4418,21 +4706,26 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
           <t>Max35Text</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
+      <c r="G70" t="inlineStr">
         <is>
           <t>Up to 35 characters.</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
+      <c r="H70" t="inlineStr">
         <is>
           <t>SVCR000000001</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr"/>
-      <c r="I70" t="n">
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4459,21 +4752,26 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
           <t>Max35Text</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
+      <c r="G71" t="inlineStr">
         <is>
           <t>Up to 35 characters.</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
+      <c r="H71" t="inlineStr">
         <is>
           <t>SAFE0000001</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr"/>
-      <c r="I71" t="n">
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4500,21 +4798,26 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
+          <t>INDICATOR</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
           <t>YesNoIndicator</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
+      <c r="G72" t="inlineStr">
         <is>
           <t>true or false.</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
+      <c r="H72" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr"/>
-      <c r="I72" t="n">
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4541,25 +4844,30 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
+          <t>SELECT</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
           <t>Code</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
+      <c r="G73" t="inlineStr">
         <is>
           <t>One of: CDPD, CLAT, CONF, MONY, SDUT, WAIT</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
+      <c r="H73" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
+      <c r="I73" t="inlineStr">
         <is>
           <t>CDPD, CLAT, CONF, MONY, SDUT, WAIT</t>
         </is>
       </c>
-      <c r="I73" t="n">
+      <c r="J73" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4586,21 +4894,26 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
+          <t>DATE</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
           <t>ISODate</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
+      <c r="G74" t="inlineStr">
         <is>
           <t>An ISO date, YYYY-MM-DD.</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
+      <c r="H74" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr"/>
-      <c r="I74" t="n">
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4627,25 +4940,30 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
+          <t>SELECT</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
           <t>Code</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
+      <c r="G75" t="inlineStr">
         <is>
           <t>One of: NPAR, PAR, PARC, PARQ</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
+      <c r="H75" t="inlineStr">
         <is>
           <t>PAR</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
+      <c r="I75" t="inlineStr">
         <is>
           <t>NPAR, PAR, PARC, PARQ</t>
         </is>
       </c>
-      <c r="I75" t="n">
+      <c r="J75" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4672,25 +4990,30 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
+          <t>SELECT</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
           <t>Code</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
+      <c r="G76" t="inlineStr">
         <is>
           <t>One of: AFTE, WITH, BEFO, INFO</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr">
+      <c r="H76" t="inlineStr">
         <is>
           <t>WITH</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
+      <c r="I76" t="inlineStr">
         <is>
           <t>AFTE, WITH, BEFO, INFO</t>
         </is>
       </c>
-      <c r="I76" t="n">
+      <c r="J76" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4717,21 +5040,26 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
           <t>Max35Text</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
+      <c r="G77" t="inlineStr">
         <is>
           <t>Up to 35 characters.</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
+      <c r="H77" t="inlineStr">
         <is>
           <t>TESTREF002</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr"/>
-      <c r="I77" t="n">
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4758,21 +5086,26 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
           <t>Max350Text</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
+      <c r="G78" t="inlineStr">
         <is>
           <t>Up to 350 characters.</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr">
+      <c r="H78" t="inlineStr">
         <is>
           <t>RELEASE FOR SETTLEMENT - FUNDING CONFIRMED</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr"/>
-      <c r="I78" t="n">
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4799,21 +5132,26 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
           <t>Max35Text</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr">
         <is>
           <t>Up to 35 characters.</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr">
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>MODREQ0000001</t>
         </is>
       </c>
-      <c r="H79" s="2" t="inlineStr"/>
-      <c r="I79" s="2" t="n">
+      <c r="I79" s="2" t="inlineStr"/>
+      <c r="J79" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4840,21 +5178,26 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
           <t>Max35Text</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr">
         <is>
           <t>Up to 35 characters.</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr">
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>TESTREF001</t>
         </is>
       </c>
-      <c r="H80" s="2" t="inlineStr"/>
-      <c r="I80" s="2" t="n">
+      <c r="I80" s="2" t="inlineStr"/>
+      <c r="J80" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4881,21 +5224,26 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
           <t>Max35Text</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
+      <c r="G81" t="inlineStr">
         <is>
           <t>Up to 35 characters.</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr">
+      <c r="H81" t="inlineStr">
         <is>
           <t>SVCR000000001</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr"/>
-      <c r="I81" t="n">
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4922,21 +5270,26 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
           <t>Max35Text</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
+      <c r="G82" t="inlineStr">
         <is>
           <t>Up to 35 characters.</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
+      <c r="H82" t="inlineStr">
         <is>
           <t>SAFE0000001</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr"/>
-      <c r="I82" t="n">
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4963,25 +5316,30 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
+          <t>SELECT</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
           <t>Code</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr">
+      <c r="G83" t="inlineStr">
         <is>
           <t>One of: NORE</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr">
+      <c r="H83" t="inlineStr">
         <is>
           <t>NORE</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
+      <c r="I83" t="inlineStr">
         <is>
           <t>NORE</t>
         </is>
       </c>
-      <c r="I83" t="n">
+      <c r="J83" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5008,25 +5366,30 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
+          <t>SELECT</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
           <t>Code</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr">
+      <c r="G84" t="inlineStr">
         <is>
           <t>One of: NORE</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr">
+      <c r="H84" t="inlineStr">
         <is>
           <t>NORE</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
+      <c r="I84" t="inlineStr">
         <is>
           <t>NORE</t>
         </is>
       </c>
-      <c r="I84" t="n">
+      <c r="J84" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5053,25 +5416,30 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
+          <t>SELECT</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
           <t>Code</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
+      <c r="G85" t="inlineStr">
         <is>
           <t>One of: ADEA, CDRE, CDPD, CVAL, LATE, NARR, OTHR</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr">
+      <c r="H85" t="inlineStr">
         <is>
           <t>LATE</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
+      <c r="I85" t="inlineStr">
         <is>
           <t>ADEA, CDRE, CDPD, CVAL, LATE, NARR, OTHR</t>
         </is>
       </c>
-      <c r="I85" t="n">
+      <c r="J85" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5098,21 +5466,26 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
           <t>Max350Text</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr">
+      <c r="G86" t="inlineStr">
         <is>
           <t>Up to 350 characters.</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr">
+      <c r="H86" t="inlineStr">
         <is>
           <t>AWAITING COUNTERPARTY CONFIRMATION</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr"/>
-      <c r="I86" t="n">
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5139,25 +5512,30 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
+          <t>SELECT</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
           <t>Code</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr">
+      <c r="G87" t="inlineStr">
         <is>
           <t>One of: ADEA, DSEC, LATE, NRGN, REFE, SAFE, ULNK, OTHR</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr">
+      <c r="H87" t="inlineStr">
         <is>
           <t>REFE</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
+      <c r="I87" t="inlineStr">
         <is>
           <t>ADEA, DSEC, LATE, NRGN, REFE, SAFE, ULNK, OTHR</t>
         </is>
       </c>
-      <c r="I87" t="n">
+      <c r="J87" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5184,21 +5562,26 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
           <t>Max350Text</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr">
+      <c r="G88" t="inlineStr">
         <is>
           <t>Up to 350 characters.</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr">
+      <c r="H88" t="inlineStr">
         <is>
           <t>NO TRANSACTION FOUND FOR REFERENCE TESTREF001</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr"/>
-      <c r="I88" t="n">
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5225,25 +5608,30 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
+          <t>SELECT</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
           <t>Code</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr">
+      <c r="G89" t="inlineStr">
         <is>
           <t>One of: ADEA, DCAN, DPRG, DSET, LATE, OTHR</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr">
+      <c r="H89" t="inlineStr">
         <is>
           <t>DSET</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
+      <c r="I89" t="inlineStr">
         <is>
           <t>ADEA, DCAN, DPRG, DSET, LATE, OTHR</t>
         </is>
       </c>
-      <c r="I89" t="n">
+      <c r="J89" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5270,26 +5658,31 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
           <t>Max350Text</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr">
+      <c r="G90" t="inlineStr">
         <is>
           <t>Up to 350 characters.</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr">
+      <c r="H90" t="inlineStr">
         <is>
           <t>TRANSACTION SETTLED AT 09:15 ON 2026-08-18</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr"/>
-      <c r="I90" t="n">
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="n">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I90"/>
+  <autoFilter ref="A1:J90"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5300,7 +5693,4546 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:F159"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="67" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="27" customWidth="1" min="5" max="5"/>
+    <col width="70" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>MessageType</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>XPath</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Means</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>sese.020</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>/Document/SctiesMsgCxlAdvc/TxDtls/SctiesMvmntTp</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Securities Movement Type</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>RECE</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>RECE</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>sese.020</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>/Document/SctiesMsgCxlAdvc/TxDtls/SctiesMvmntTp</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Securities Movement Type</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>DELI</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>DELI</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>sese.023</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxInstr/SttlmTpAndAddtlParams/SctiesMvmntTp</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Securities Movement Type</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>RECE</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Receive</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Securities are received into the account.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>sese.023</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxInstr/SttlmTpAndAddtlParams/SctiesMvmntTp</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Securities Movement Type</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>DELI</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Deliver</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Securities are delivered out of the account.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>sese.023</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxInstr/SttlmTpAndAddtlParams/Pmt</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Payment</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>APMT</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Against Payment</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Cash is paid against the securities. A settlement amount is required.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>sese.023</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxInstr/SttlmTpAndAddtlParams/Pmt</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Payment</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Free of Payment</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Securities move with no cash leg. No settlement amount is carried.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>sese.023</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxInstr/SttlmParams/SctiesTxTp/Cd</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Transaction Type Code</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>TRAD</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Trade</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Settlement of an ordinary secondary-market trade. The usual choice.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>sese.023</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxInstr/SttlmParams/SctiesTxTp/Cd</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Transaction Type Code</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>COLI</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Collateral In</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Securities received as collateral.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>sese.023</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxInstr/SttlmParams/SctiesTxTp/Cd</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Transaction Type Code</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>COLO</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Collateral Out</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Securities delivered as collateral.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>sese.023</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxInstr/SttlmParams/SctiesTxTp/Cd</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Transaction Type Code</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>PLAC</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Placement</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Placement of securities.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>sese.023</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxInstr/SttlmParams/SctiesTxTp/Cd</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Transaction Type Code</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>PORT</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Portfolio Move</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Movement of a portfolio between accounts or account servicers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>sese.023</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxInstr/SttlmParams/SctiesTxTp/Cd</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Transaction Type Code</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>REDM</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Redemption</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Redemption of a fund holding or a maturing instrument.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>sese.023</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxInstr/SttlmParams/SctiesTxTp/Cd</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Transaction Type Code</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>SUBS</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Subscription</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Subscription to a fund or a new issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>sese.023</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxInstr/SttlmParams/SctiesTxTp/Cd</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Transaction Type Code</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>TURN</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Turnaround</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Securities bought and sold for settlement on the same day.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sese.023</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxInstr/SttlmParams/SctiesTxTp/Cd</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Transaction Type Code</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NETT</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Netting</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Settlement of a netted position rather than of each trade.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>sese.023</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxInstr/SttlmParams/SctiesTxTp/Cd</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Transaction Type Code</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>OWNE</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>External Account Transfer</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Transfer between accounts with different account servicers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>sese.023</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxInstr/SttlmParams/SctiesTxTp/Cd</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Transaction Type Code</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>OWNI</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Internal Account Transfer</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Transfer between accounts with the same account servicer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>sese.023</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxInstr/SttlmParams/SttlmTxCond/Cd</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Settlement Condition Code</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NOMC</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>NOMC</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>sese.023</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxInstr/SttlmParams/SttlmTxCond/Cd</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Settlement Condition Code</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>PART</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>PART</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>sese.023</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxInstr/SttlmParams/SttlmTxCond/Cd</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Settlement Condition Code</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>PARC</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>PARC</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>sese.023</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxInstr/SttlmParams/SttlmTxCond/Cd</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Settlement Condition Code</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>PARQ</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>PARQ</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>sese.023</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxInstr/SttlmParams/SttlmTxCond/Cd</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Settlement Condition Code</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>ASGN</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>ASGN</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>sese.023</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxInstr/SttlmParams/SttlmTxCond/Cd</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Settlement Condition Code</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>BLOC</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>BLOC</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>sese.023</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxInstr/SttlmParams/SttlmTxCond/Cd</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Settlement Condition Code</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>CLEN</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>CLEN</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>sese.023</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxInstr/SttlmParams/SttlmTxCond/Cd</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Settlement Condition Code</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>DIRT</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>DIRT</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>sese.023</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxInstr/SttlmParams/SttlmTxCond/Cd</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Settlement Condition Code</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>DLWM</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>DLWM</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>sese.023</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxInstr/SttlmParams/SttlmTxCond/Cd</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Settlement Condition Code</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>PHYS</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>PHYS</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>sese.023</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxInstr/SttlmParams/SttlmTxCond/Cd</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Settlement Condition Code</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>SPDL</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>SPDL</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>sese.023</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxInstr/SttlmAmt/CdtDbtInd</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Credit or Debit Indicator</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>CRDT</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>CRDT</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>sese.023</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxInstr/SttlmAmt/CdtDbtInd</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Credit or Debit Indicator</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>DBIT</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>DBIT</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>sese.024</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxStsAdvc/TxIdDtls/SctiesMvmntTp</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Securities Movement Type</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>RECE</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>RECE</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>sese.024</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxStsAdvc/TxIdDtls/SctiesMvmntTp</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Securities Movement Type</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>DELI</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>DELI</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>sese.024</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxStsAdvc/TxIdDtls/Pmt</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Payment</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>APMT</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>APMT</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>sese.024</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxStsAdvc/TxIdDtls/Pmt</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Payment</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>sese.024</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxStsAdvc/PrcgSts/AckdAccptd/NoSpcfdRsn</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>No Specified Reason</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NORE</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>NORE</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>sese.024</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxStsAdvc/PrcgSts/PdgPrcg/Rsn/Cd/Cd</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Pending Processing Reason Code</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>AWMO</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>AWMO</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>sese.024</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxStsAdvc/PrcgSts/PdgPrcg/Rsn/Cd/Cd</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Pending Processing Reason Code</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>AWSH</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>AWSH</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>sese.024</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxStsAdvc/PrcgSts/PdgPrcg/Rsn/Cd/Cd</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Pending Processing Reason Code</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>BATC</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>BATC</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>sese.024</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxStsAdvc/PrcgSts/PdgPrcg/Rsn/Cd/Cd</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Pending Processing Reason Code</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>CAIS</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>CAIS</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>sese.024</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxStsAdvc/PrcgSts/PdgPrcg/Rsn/Cd/Cd</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Pending Processing Reason Code</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>CYCL</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>CYCL</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>sese.024</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxStsAdvc/PrcgSts/PdgPrcg/Rsn/Cd/Cd</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Pending Processing Reason Code</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>DOCC</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>DOCC</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>sese.024</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxStsAdvc/PrcgSts/PdgPrcg/Rsn/Cd/Cd</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Pending Processing Reason Code</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>DOCY</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>DOCY</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>sese.024</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxStsAdvc/PrcgSts/PdgPrcg/Rsn/Cd/Cd</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Pending Processing Reason Code</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>FUTU</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>FUTU</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>sese.024</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxStsAdvc/PrcgSts/PdgPrcg/Rsn/Cd/Cd</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Pending Processing Reason Code</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LACK</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>LACK</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>sese.024</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxStsAdvc/PrcgSts/PdgPrcg/Rsn/Cd/Cd</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Pending Processing Reason Code</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LATE</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>LATE</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>sese.024</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxStsAdvc/PrcgSts/PdgPrcg/Rsn/Cd/Cd</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Pending Processing Reason Code</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NEXT</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>NEXT</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>sese.024</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxStsAdvc/PrcgSts/PdgPrcg/Rsn/Cd/Cd</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Pending Processing Reason Code</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>OTHR</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>OTHR</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>sese.024</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxStsAdvc/PrcgSts/Rjctd/Rsn/Cd/Cd</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Rejection Reason Code</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>CASH</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>CASH</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>sese.024</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxStsAdvc/PrcgSts/Rjctd/Rsn/Cd/Cd</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Rejection Reason Code</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>DDAT</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>DDAT</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>sese.024</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxStsAdvc/PrcgSts/Rjctd/Rsn/Cd/Cd</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Rejection Reason Code</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>DQUA</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>DQUA</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>sese.024</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxStsAdvc/PrcgSts/Rjctd/Rsn/Cd/Cd</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Rejection Reason Code</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>DSEC</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>DSEC</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>sese.024</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxStsAdvc/PrcgSts/Rjctd/Rsn/Cd/Cd</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Rejection Reason Code</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>ICAG</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>ICAG</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>sese.024</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxStsAdvc/PrcgSts/Rjctd/Rsn/Cd/Cd</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Rejection Reason Code</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>ICUS</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>ICUS</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>sese.024</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxStsAdvc/PrcgSts/Rjctd/Rsn/Cd/Cd</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Rejection Reason Code</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>IEXE</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>IEXE</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>sese.024</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxStsAdvc/PrcgSts/Rjctd/Rsn/Cd/Cd</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Rejection Reason Code</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>INVB</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>INVB</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>sese.024</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxStsAdvc/PrcgSts/Rjctd/Rsn/Cd/Cd</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Rejection Reason Code</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NCRR</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>NCRR</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>sese.024</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxStsAdvc/PrcgSts/Rjctd/Rsn/Cd/Cd</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Rejection Reason Code</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>REFE</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>REFE</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>sese.024</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxStsAdvc/PrcgSts/Rjctd/Rsn/Cd/Cd</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Rejection Reason Code</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>sese.024</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxStsAdvc/PrcgSts/Rjctd/Rsn/Cd/Cd</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Rejection Reason Code</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>SETS</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>SETS</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>sese.024</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxStsAdvc/PrcgSts/Rjctd/Rsn/Cd/Cd</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Rejection Reason Code</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>OTHR</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>OTHR</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>sese.024</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxStsAdvc/PrcgSts/Canc/Rsn/Cd/Cd</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Cancellation Reason Code</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>CANI</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>CANI</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>sese.024</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxStsAdvc/PrcgSts/Canc/Rsn/Cd/Cd</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Cancellation Reason Code</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>CANS</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>CANS</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>sese.024</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxStsAdvc/PrcgSts/Canc/Rsn/Cd/Cd</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Cancellation Reason Code</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>CSUB</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>CSUB</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>sese.024</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxStsAdvc/PrcgSts/Canc/Rsn/Cd/Cd</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Cancellation Reason Code</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>CANT</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>CANT</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>sese.024</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxStsAdvc/PrcgSts/Canc/Rsn/Cd/Cd</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Cancellation Reason Code</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>CANZ</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>CANZ</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>sese.024</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxStsAdvc/PrcgSts/Canc/Rsn/Cd/Cd</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Cancellation Reason Code</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>CORP</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>CORP</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>sese.024</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxStsAdvc/PrcgSts/Canc/Rsn/Cd/Cd</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Cancellation Reason Code</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>SCEX</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>SCEX</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>sese.024</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxStsAdvc/PrcgSts/Canc/Rsn/Cd/Cd</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Cancellation Reason Code</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>OTHR</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>OTHR</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>sese.024</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxStsAdvc/MtchgSts/Mtchd</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Matched</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>MACH</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>MACH</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>sese.024</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxStsAdvc/MtchgSts/Umtchd/Rsn/Cd/Cd</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Unmatched Reason Code</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>CMIS</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>CMIS</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>sese.024</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxStsAdvc/MtchgSts/Umtchd/Rsn/Cd/Cd</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Unmatched Reason Code</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>DDAT</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>DDAT</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>sese.024</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxStsAdvc/MtchgSts/Umtchd/Rsn/Cd/Cd</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Unmatched Reason Code</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>DDEA</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>DDEA</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>sese.024</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxStsAdvc/MtchgSts/Umtchd/Rsn/Cd/Cd</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Unmatched Reason Code</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>DELN</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>DELN</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>sese.024</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxStsAdvc/MtchgSts/Umtchd/Rsn/Cd/Cd</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Unmatched Reason Code</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>DEPT</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>DEPT</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>sese.024</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxStsAdvc/MtchgSts/Umtchd/Rsn/Cd/Cd</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Unmatched Reason Code</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>DMON</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>DMON</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>sese.024</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxStsAdvc/MtchgSts/Umtchd/Rsn/Cd/Cd</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Unmatched Reason Code</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>DQUA</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>DQUA</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>sese.024</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxStsAdvc/MtchgSts/Umtchd/Rsn/Cd/Cd</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Unmatched Reason Code</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>DSEC</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>DSEC</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>sese.024</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxStsAdvc/MtchgSts/Umtchd/Rsn/Cd/Cd</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Unmatched Reason Code</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>DTRD</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>DTRD</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>sese.024</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxStsAdvc/MtchgSts/Umtchd/Rsn/Cd/Cd</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Unmatched Reason Code</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NMAS</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>NMAS</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>sese.024</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxStsAdvc/MtchgSts/Umtchd/Rsn/Cd/Cd</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Unmatched Reason Code</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>sese.024</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxStsAdvc/MtchgSts/Umtchd/Rsn/Cd/Cd</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Unmatched Reason Code</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>OTHR</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>OTHR</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>sese.024</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxStsAdvc/SttlmSts/Pdg/Rsn/Cd/Cd</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Pending Settlement Reason Code</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>AWMO</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>AWMO</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>sese.024</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxStsAdvc/SttlmSts/Pdg/Rsn/Cd/Cd</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Pending Settlement Reason Code</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>AWSH</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>AWSH</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>sese.024</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxStsAdvc/SttlmSts/Pdg/Rsn/Cd/Cd</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Pending Settlement Reason Code</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>CAIS</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>CAIS</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>sese.024</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxStsAdvc/SttlmSts/Pdg/Rsn/Cd/Cd</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Pending Settlement Reason Code</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>CLAC</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>CLAC</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>sese.024</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxStsAdvc/SttlmSts/Pdg/Rsn/Cd/Cd</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Pending Settlement Reason Code</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>CMON</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>CMON</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>sese.024</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxStsAdvc/SttlmSts/Pdg/Rsn/Cd/Cd</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Pending Settlement Reason Code</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>CYCL</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>CYCL</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>sese.024</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxStsAdvc/SttlmSts/Pdg/Rsn/Cd/Cd</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Pending Settlement Reason Code</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>LACK</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>LACK</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>sese.024</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxStsAdvc/SttlmSts/Pdg/Rsn/Cd/Cd</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Pending Settlement Reason Code</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>LATE</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>LATE</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>sese.024</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxStsAdvc/SttlmSts/Pdg/Rsn/Cd/Cd</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Pending Settlement Reason Code</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>MONY</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>MONY</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>sese.024</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxStsAdvc/SttlmSts/Pdg/Rsn/Cd/Cd</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Pending Settlement Reason Code</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>PREA</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>PREA</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>sese.024</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxStsAdvc/SttlmSts/Pdg/Rsn/Cd/Cd</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Pending Settlement Reason Code</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>OTHR</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>OTHR</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>sese.024</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxStsAdvc/SttlmSts/Flng/Rsn/Cd/Cd</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Failing Reason Code</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>AWMO</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>AWMO</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>sese.024</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxStsAdvc/SttlmSts/Flng/Rsn/Cd/Cd</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Failing Reason Code</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>AWSH</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>AWSH</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>sese.024</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxStsAdvc/SttlmSts/Flng/Rsn/Cd/Cd</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Failing Reason Code</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>CLAC</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>CLAC</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>sese.024</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxStsAdvc/SttlmSts/Flng/Rsn/Cd/Cd</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Failing Reason Code</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>CMON</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>CMON</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>sese.024</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxStsAdvc/SttlmSts/Flng/Rsn/Cd/Cd</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Failing Reason Code</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>LACK</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>LACK</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>sese.024</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxStsAdvc/SttlmSts/Flng/Rsn/Cd/Cd</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Failing Reason Code</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>LATE</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>LATE</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>sese.024</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxStsAdvc/SttlmSts/Flng/Rsn/Cd/Cd</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Failing Reason Code</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>MONY</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>MONY</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>sese.024</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxStsAdvc/SttlmSts/Flng/Rsn/Cd/Cd</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Failing Reason Code</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>OTHR</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>OTHR</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>sese.025</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxConf/TxIdDtls/SctiesMvmntTp</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Securities Movement Type</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>RECE</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>RECE</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>sese.025</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxConf/TxIdDtls/SctiesMvmntTp</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Securities Movement Type</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>DELI</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>DELI</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>sese.025</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxConf/TxIdDtls/Pmt</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Payment</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>APMT</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>APMT</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>sese.025</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxConf/TxIdDtls/Pmt</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Payment</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>sese.025</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxConf/SttlmParams/SctiesTxTp/Cd</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Transaction Type Code</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>TRAD</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>TRAD</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>sese.025</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxConf/SttlmParams/SctiesTxTp/Cd</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Transaction Type Code</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>COLI</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>COLI</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>sese.025</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxConf/SttlmParams/SctiesTxTp/Cd</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Transaction Type Code</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>COLO</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>COLO</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>sese.025</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxConf/SttlmParams/SctiesTxTp/Cd</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Transaction Type Code</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>PLAC</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>PLAC</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>sese.025</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxConf/SttlmParams/SctiesTxTp/Cd</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Transaction Type Code</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>PORT</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>PORT</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>sese.025</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxConf/SttlmParams/SctiesTxTp/Cd</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Transaction Type Code</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>REDM</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>REDM</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>sese.025</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxConf/SttlmParams/SctiesTxTp/Cd</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Transaction Type Code</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>SUBS</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>SUBS</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>sese.025</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxConf/SttlmParams/SctiesTxTp/Cd</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Transaction Type Code</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>TURN</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>TURN</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>sese.025</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxConf/SttlmParams/SctiesTxTp/Cd</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Transaction Type Code</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>NETT</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>NETT</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>sese.025</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxConf/SttlmParams/SctiesTxTp/Cd</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Transaction Type Code</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>OWNE</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>OWNE</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>sese.025</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxConf/SttlmParams/SctiesTxTp/Cd</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Transaction Type Code</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>OWNI</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>OWNI</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>sese.025</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxConf/SttlmAmt/CdtDbtInd</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Credit or Debit Indicator</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>CRDT</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>CRDT</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>sese.025</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmTxConf/SttlmAmt/CdtDbtInd</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Credit or Debit Indicator</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>DBIT</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>DBIT</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>sese.027</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>/Document/SctiesTxCxlReq/TxDtls/SctiesMvmntTp</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Securities Movement Type</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>RECE</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>RECE</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>sese.027</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>/Document/SctiesTxCxlReq/TxDtls/SctiesMvmntTp</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Securities Movement Type</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>DELI</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>DELI</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>sese.027</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>/Document/SctiesTxCxlReq/TxDtls/Pmt</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Payment</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>APMT</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>APMT</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>sese.027</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>/Document/SctiesTxCxlReq/TxDtls/Pmt</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Payment</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>sese.030</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmCondsModReq/HldInd/Rsn</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Hold Reason</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>CDPD</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>CDPD</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>sese.030</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmCondsModReq/HldInd/Rsn</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Hold Reason</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>CLAT</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>CLAT</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>sese.030</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmCondsModReq/HldInd/Rsn</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Hold Reason</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>CONF</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>CONF</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>sese.030</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmCondsModReq/HldInd/Rsn</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Hold Reason</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>MONY</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>MONY</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>sese.030</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmCondsModReq/HldInd/Rsn</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Hold Reason</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>SDUT</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>SDUT</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>sese.030</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmCondsModReq/HldInd/Rsn</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Hold Reason</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>WAIT</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>WAIT</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>sese.030</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmCondsModReq/PrtlSttlmInd/Cd</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Partial Settlement Code</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>NPAR</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>NPAR</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>sese.030</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmCondsModReq/PrtlSttlmInd/Cd</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Partial Settlement Code</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>PAR</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>PAR</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>sese.030</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmCondsModReq/PrtlSttlmInd/Cd</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Partial Settlement Code</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>PARC</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>PARC</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>sese.030</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmCondsModReq/PrtlSttlmInd/Cd</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Partial Settlement Code</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>PARQ</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>PARQ</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>sese.030</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmCondsModReq/Lnkgs/PrcgPos</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Processing Position</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>AFTE</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>AFTE</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>sese.030</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmCondsModReq/Lnkgs/PrcgPos</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Processing Position</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>WITH</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>WITH</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>sese.030</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmCondsModReq/Lnkgs/PrcgPos</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Processing Position</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>BEFO</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>BEFO</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>sese.030</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmCondsModReq/Lnkgs/PrcgPos</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Processing Position</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>sese.031</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmCondModStsAdvc/PrcgSts/Cmpltd/NoSpcfdRsn</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>No Specified Reason</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>NORE</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>NORE</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>sese.031</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmCondModStsAdvc/PrcgSts/AckdAccptd/NoSpcfdRsn</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>No Specified Reason</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>NORE</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>NORE</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>sese.031</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmCondModStsAdvc/PrcgSts/Pdg/Rsn</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Pending Reason</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>ADEA</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>ADEA</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>sese.031</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmCondModStsAdvc/PrcgSts/Pdg/Rsn</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Pending Reason</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>CDRE</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>CDRE</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>sese.031</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmCondModStsAdvc/PrcgSts/Pdg/Rsn</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Pending Reason</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>CDPD</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>CDPD</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>sese.031</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmCondModStsAdvc/PrcgSts/Pdg/Rsn</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Pending Reason</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>CVAL</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>CVAL</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>sese.031</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmCondModStsAdvc/PrcgSts/Pdg/Rsn</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Pending Reason</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>LATE</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>LATE</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>sese.031</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmCondModStsAdvc/PrcgSts/Pdg/Rsn</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Pending Reason</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>NARR</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>NARR</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>sese.031</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmCondModStsAdvc/PrcgSts/Pdg/Rsn</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Pending Reason</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>OTHR</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>OTHR</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>sese.031</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmCondModStsAdvc/PrcgSts/Rjctd/Rsn</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Rejection Reason</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>ADEA</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>ADEA</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>sese.031</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmCondModStsAdvc/PrcgSts/Rjctd/Rsn</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Rejection Reason</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>DSEC</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>DSEC</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>sese.031</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmCondModStsAdvc/PrcgSts/Rjctd/Rsn</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Rejection Reason</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>LATE</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>LATE</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>sese.031</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmCondModStsAdvc/PrcgSts/Rjctd/Rsn</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Rejection Reason</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>NRGN</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>NRGN</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>sese.031</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmCondModStsAdvc/PrcgSts/Rjctd/Rsn</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Rejection Reason</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>REFE</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>REFE</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>sese.031</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmCondModStsAdvc/PrcgSts/Rjctd/Rsn</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Rejection Reason</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>sese.031</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmCondModStsAdvc/PrcgSts/Rjctd/Rsn</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Rejection Reason</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>ULNK</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>ULNK</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>sese.031</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmCondModStsAdvc/PrcgSts/Rjctd/Rsn</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Rejection Reason</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>OTHR</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>OTHR</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>sese.031</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmCondModStsAdvc/PrcgSts/Dnd/Rsn</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Denial Reason</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>ADEA</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>ADEA</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>sese.031</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmCondModStsAdvc/PrcgSts/Dnd/Rsn</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Denial Reason</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>DCAN</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>DCAN</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>sese.031</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmCondModStsAdvc/PrcgSts/Dnd/Rsn</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Denial Reason</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>DPRG</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>DPRG</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>sese.031</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmCondModStsAdvc/PrcgSts/Dnd/Rsn</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Denial Reason</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>DSET</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>DSET</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>sese.031</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmCondModStsAdvc/PrcgSts/Dnd/Rsn</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Denial Reason</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>LATE</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>LATE</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>sese.031</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>/Document/SctiesSttlmCondModStsAdvc/PrcgSts/Dnd/Rsn</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Denial Reason</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>OTHR</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>OTHR</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F159"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="70" customWidth="1" min="1" max="1"/>
@@ -5430,7 +10362,7 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>4. Upload the workbook to POST /api/v1/messages/generate-from-excel.</t>
+          <t>4. Cells with a dropdown accept only the codes on the Codes sheet.</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr"/>
@@ -5438,13 +10370,93 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>5. The response contains the generated message and per-scenario validation.</t>
+          <t>5. Upload the workbook to POST /api/v1/messages/generate-from-excel.</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr"/>
     </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>6. The response contains the generated message and per-scenario validation.</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="n"/>
+      <c r="B16" s="4" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>What goes in the Value column</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Business values, not SWIFT syntax</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Enter what the field means. The studio writes the SWIFT rendering.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Financial instrument (35B)</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Enter the 12-character identifier only, for example XS0000000009. Do NOT type the word ISIN — the studio writes it. A value that arrives with the prefix already on it is accepted and normalised, so an older sheet keeps working.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Settlement parties (95a)</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>Use tag 95P and a BIC to identify a party by its Business Identifier Code. Use 95R and a data source scheme with the identifier, such as CSD/DEMOPSET01, for a proprietary code. Do not put a BIC in a 95R value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Controlled codes</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Use the Code column on the Codes sheet. The Means column is there to read, not to enter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Same values, same message</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>This workbook, the JSON API and the browser produce byte-identical output for equivalent values, because all three call the same composer.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B14"/>
+  <autoFilter ref="A1:B22"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>